--- a/00 Raw data/SDG/Publications_by_SDG_-_Taiwan.xlsx
+++ b/00 Raw data/SDG/Publications_by_SDG_-_Taiwan.xlsx
@@ -90,7 +90,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2018 to 2025</t>
+          <t>2017 to 2025</t>
         </is>
       </c>
     </row>
@@ -157,7 +157,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8 July 2026</t>
+          <t>5 August 2026</t>
         </is>
       </c>
     </row>
@@ -169,7 +169,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16 July 2026</t>
+          <t>13 August 2026</t>
         </is>
       </c>
     </row>
@@ -209,13 +209,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1140.0</v>
+        <v>1235.0</v>
       </c>
       <c r="C13" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="D13" t="n">
-        <v>15931.0</v>
+        <v>17936.0</v>
       </c>
     </row>
     <row r="14">
@@ -225,13 +225,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2803.0</v>
+        <v>2981.0</v>
       </c>
       <c r="C14" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="D14" t="n">
-        <v>71947.0</v>
+        <v>84331.0</v>
       </c>
     </row>
     <row r="15">
@@ -241,13 +241,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>66516.0</v>
+        <v>72846.0</v>
       </c>
       <c r="C15" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="D15" t="n">
-        <v>1458860.0</v>
+        <v>1743456.0</v>
       </c>
     </row>
     <row r="16">
@@ -257,13 +257,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7002.0</v>
+        <v>7586.0</v>
       </c>
       <c r="C16" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="D16" t="n">
-        <v>108944.0</v>
+        <v>123869.0</v>
       </c>
     </row>
     <row r="17">
@@ -273,13 +273,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1348.0</v>
+        <v>1428.0</v>
       </c>
       <c r="C17" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="D17" t="n">
-        <v>23236.0</v>
+        <v>34528.0</v>
       </c>
     </row>
     <row r="18">
@@ -289,13 +289,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5358.0</v>
+        <v>5732.0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="D18" t="n">
-        <v>154117.0</v>
+        <v>173511.0</v>
       </c>
     </row>
     <row r="19">
@@ -305,13 +305,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19732.0</v>
+        <v>21657.0</v>
       </c>
       <c r="C19" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="D19" t="n">
-        <v>499083.0</v>
+        <v>567156.0</v>
       </c>
     </row>
     <row r="20">
@@ -321,13 +321,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5832.0</v>
+        <v>6200.0</v>
       </c>
       <c r="C20" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="D20" t="n">
-        <v>138691.0</v>
+        <v>155676.0</v>
       </c>
     </row>
     <row r="21">
@@ -337,13 +337,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15865.0</v>
+        <v>17197.0</v>
       </c>
       <c r="C21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="D21" t="n">
-        <v>304817.0</v>
+        <v>345639.0</v>
       </c>
     </row>
     <row r="22">
@@ -353,13 +353,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2846.0</v>
+        <v>3060.0</v>
       </c>
       <c r="C22" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="D22" t="n">
-        <v>38623.0</v>
+        <v>45856.0</v>
       </c>
     </row>
     <row r="23">
@@ -369,13 +369,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7534.0</v>
+        <v>8128.0</v>
       </c>
       <c r="C23" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="D23" t="n">
-        <v>131984.0</v>
+        <v>150947.0</v>
       </c>
     </row>
     <row r="24">
@@ -385,13 +385,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6553.0</v>
+        <v>6966.0</v>
       </c>
       <c r="C24" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="D24" t="n">
-        <v>173632.0</v>
+        <v>190533.0</v>
       </c>
     </row>
     <row r="25">
@@ -401,13 +401,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6440.0</v>
+        <v>6836.0</v>
       </c>
       <c r="C25" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="D25" t="n">
-        <v>187596.0</v>
+        <v>210285.0</v>
       </c>
     </row>
     <row r="26">
@@ -417,13 +417,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3398.0</v>
+        <v>3642.0</v>
       </c>
       <c r="C26" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="D26" t="n">
-        <v>63869.0</v>
+        <v>73627.0</v>
       </c>
     </row>
     <row r="27">
@@ -433,13 +433,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2670.0</v>
+        <v>2839.0</v>
       </c>
       <c r="C27" t="n">
         <v>1.2</v>
       </c>
       <c r="D27" t="n">
-        <v>53106.0</v>
+        <v>59129.0</v>
       </c>
     </row>
     <row r="28">
@@ -449,13 +449,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2463.0</v>
+        <v>2666.0</v>
       </c>
       <c r="C28" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="D28" t="n">
-        <v>65905.0</v>
+        <v>81805.0</v>
       </c>
     </row>
     <row r="29">
@@ -465,13 +465,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>127693.0</v>
+        <v>139443.0</v>
       </c>
       <c r="C29" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="D29" t="n">
-        <v>2689277.0</v>
+        <v>3147693.0</v>
       </c>
     </row>
     <row r="30">
